--- a/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 1</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
@@ -175,16 +175,16 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>16:30 EDT</t>
+          <t>13:30 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -194,12 +194,12 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 1</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn FC #2 2013/2014</t>
+          <t>NY Kids S.C. 2013/2014 boys</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Sunday, October 18, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>13:30 EDT</t>
+          <t>12:30 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Ajer</t>
+          <t>Metropolitan Oval Academy Brooklyn 2013/14 Boys U13 Gray</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>7 - 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>NY Kids S.C. 2013/2014 boys</t>
+          <t>SC Gjoa Ajer</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field A Small Sided  - A</t>
+          <t>Red Hook Field #5 - Field 5 11v11</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,17 +259,17 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 18, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -279,7 +279,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Metropolitan Oval Academy Brooklyn 2013/14 Boys U13 Gray</t>
+          <t>SC Gjoa Ajer</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Ajer</t>
+          <t>Dynamo Soccer Club 2014</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Met Oval Field - Met Oval Field </t>
+          <t>Dyker Turf Field A Small Sided  - A</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,16 +310,16 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>13:45 EDT</t>
+          <t>13:30 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Dynamo Soccer Club 2014</t>
+          <t>South Brooklyn FC #2 2013/2014</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field A Small Sided  - A</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,7 +349,7 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-ajer.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 0</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 7</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
